--- a/results/outputs/ibd/ibd_pathway.xlsx
+++ b/results/outputs/ibd/ibd_pathway.xlsx
@@ -4518,7 +4518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4541,7 +4541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4558,143 +4558,143 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>map00120</t>
+          <t>map04148</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primary bile acid biosynthesis</t>
+          <t>Efferocytosis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>map00140</t>
+          <t>map04913</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steroid hormone biosynthesis</t>
+          <t>Ovarian steroidogenesis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>map00981</t>
+          <t>map04975</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Insect hormone biosynthesis</t>
+          <t>Fat digestion and absorption</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>map00984</t>
+          <t>map04976</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Steroid degradation</t>
+          <t>Bile secretion</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>map00996</t>
+          <t>map04977</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biosynthesis of various alkaloids</t>
+          <t>Vitamin digestion and absorption</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>map01066</t>
+          <t>map04979</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Biosynthesis of alkaloids derived from terpenoid and polyketide</t>
+          <t>Cholesterol metabolism</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>map01100</t>
+          <t>map05417</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Metabolic pathways</t>
+          <t>Lipid and atherosclerosis</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>map01120</t>
+          <t>map00100</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Microbial metabolism in diverse environments</t>
+          <t>Steroid biosynthesis</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4711,7 +4711,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4728,323 +4728,765 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>map04925</t>
+          <t>map04975</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aldosterone synthesis and secretion</t>
+          <t>Fat digestion and absorption</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>map04927</t>
+          <t>map04976</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cortisol synthesis and secretion</t>
+          <t>Bile secretion</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>map04934</t>
+          <t>map04977</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cushing syndrome</t>
+          <t>Vitamin digestion and absorption</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>map04975</t>
+          <t>map04979</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fat digestion and absorption</t>
+          <t>Cholesterol metabolism</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>map04976</t>
+          <t>map05417</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bile secretion</t>
+          <t>Lipid and atherosclerosis</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>map04977</t>
+          <t>map00100</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vitamin digestion and absorption</t>
+          <t>Steroid biosynthesis</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>map04979</t>
+          <t>map04148</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cholesterol metabolism</t>
+          <t>Efferocytosis</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>map05200</t>
+          <t>map04913</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pathways in cancer</t>
+          <t>Ovarian steroidogenesis</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>map05217</t>
+          <t>map04975</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Basal cell carcinoma</t>
+          <t>Fat digestion and absorption</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C00187</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>map05417</t>
+          <t>map04976</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lipid and atherosclerosis</t>
+          <t>Bile secretion</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C00157</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>map00564</t>
+          <t>map04977</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Glycerophospholipid metabolism</t>
+          <t>Vitamin digestion and absorption</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C00157</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>map00590</t>
+          <t>map04979</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arachidonic acid metabolism</t>
+          <t>Cholesterol metabolism</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C00157</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>map00591</t>
+          <t>map05417</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Linoleic acid metabolism</t>
+          <t>Lipid and atherosclerosis</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C00157</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>map00592</t>
+          <t>map00100</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>alpha-Linolenic acid metabolism</t>
+          <t>Steroid biosynthesis</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C00157</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>map01100</t>
+          <t>map04148</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Metabolic pathways</t>
+          <t>Efferocytosis</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C00157</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>map01110</t>
+          <t>map04913</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Biosynthesis of secondary metabolites</t>
+          <t>Ovarian steroidogenesis</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C00157</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>map04723</t>
+          <t>map04975</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Retrograde endocannabinoid signaling</t>
+          <t>Fat digestion and absorption</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C00157</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>map04981</t>
+          <t>map04976</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Folate transport and metabolism</t>
+          <t>Bile secretion</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C00157</t>
+          <t>C02530</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>map05231</t>
+          <t>map04977</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Choline metabolism in cancer</t>
+          <t>Vitamin digestion and absorption</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>map04979</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cholesterol metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>map05417</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Lipid and atherosclerosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>map00100</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Steroid biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>map04148</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Efferocytosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>map04913</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovarian steroidogenesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>map04975</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fat digestion and absorption</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>map04976</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bile secretion</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>map04977</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Vitamin digestion and absorption</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>map04979</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cholesterol metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>map05417</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Lipid and atherosclerosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>map00100</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Steroid biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>map04148</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Efferocytosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>map04913</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovarian steroidogenesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>map04975</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fat digestion and absorption</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>map04976</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bile secretion</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>map04977</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Vitamin digestion and absorption</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>map04979</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cholesterol metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>map05417</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Lipid and atherosclerosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>map00100</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Steroid biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>map04148</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Efferocytosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>map04913</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovarian steroidogenesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>map04975</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Fat digestion and absorption</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>map04976</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bile secretion</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>map04977</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Vitamin digestion and absorption</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>map04979</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Cholesterol metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C02530</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>map05417</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Lipid and atherosclerosis</t>
         </is>
       </c>
     </row>
